--- a/data/output/reporte_moldeo.xlsx
+++ b/data/output/reporte_moldeo.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,27 +27,15 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -76,18 +64,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -455,187 +440,310 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="96" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="96" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha/Hora Proceso</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID de Correo / Origen</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Fecha del Correo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>Turno</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Máquina ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Líder de Turno</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Paro (Minutos)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Piezas Aprobadas</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Piezas Rechazadas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Motivos / Observaciones</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Archivo Origen</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10 05:58:30</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Turno 1</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gmail_1a08a263d99ac53d</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-10 07:15:35</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Turno 2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>M102</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Juan Pérez</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>cambio de molde, defectos estéticos, revisiones preventivas completadas</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>turno1_estandar.txt</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Luis Hernández</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>rayones</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10 05:59:21</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Turno 3</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>M103</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Francisco Ruiz</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1120</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>ajuste de presión hidráulica, desalineación de guías, porosidad interna, marcas de inyección</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Entrada Manual</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gmail_1a08a263d99ac53d</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-10 07:15:35</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Turno 2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>M104</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Luis Hernández</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G3" t="n">
+        <v>900</v>
+      </c>
+      <c r="H3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>falla eléctrica, fuera de tolerancia dimensional</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10 06:01:22</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gmail_1a08a2de1aeea353</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-10 07:17:46</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>M103</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Roberto Sánchez</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1350</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cambio de molde rápido, mal color</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gmail_1a08c569f38a04a5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:24:05</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Turno 2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>M107</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Daniela Morales</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1890</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>limpieza de boquilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gmail_1a08ca13c36eefef</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-10 18:42:57</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Turno 5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>M110</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Daniela Morales</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1190</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>limpieza de boquilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>1a08d48dd9af1e8d</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 15:45:44 -0600</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>Turno 3</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>M108</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Ana Torres</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>980</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>sobrecalentamiento del motor, falta de lubricación, vibración extraña</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Entrada Manual</t>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>M103</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Francisco Ruiz</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1120</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>ajuste de presión hidráulica, desalineación de guías, porosidad interna, marcas de inyección</t>
         </is>
       </c>
     </row>
